--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_With_Decisions.xlsx
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -636,7 +636,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_With_Decisions.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -611,7 +611,7 @@
   </si>
   <si>
     <t xml:space="preserve">• Enrollment -8 cumulative
-• Tuition $-500/student</t>
+• Tuition -$500/student</t>
   </si>
   <si>
     <t>Board declined; enrollment goals retained as originally modeled.</t>
@@ -636,7 +636,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -759,7 +759,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1999,7 +1999,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2009,7 +2009,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
         <v>194</v>
       </c>
@@ -2019,8 +2019,9 @@
       <c r="F2" s="42"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="57" t="s">
         <v>195</v>
       </c>
@@ -2030,6 +2031,7 @@
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
       <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="58" t="s">
@@ -2520,7 +2522,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>229</v>
       </c>
@@ -2536,8 +2538,9 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="78" t="s">
         <v>233</v>
       </c>
@@ -2553,8 +2556,9 @@
       </c>
       <c r="G30" s="80"/>
       <c r="H30" s="80"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="80"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="78" t="s">
         <v>237</v>
       </c>
@@ -2570,8 +2574,9 @@
       </c>
       <c r="G31" s="80"/>
       <c r="H31" s="80"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="80"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="78" t="s">
         <v>240</v>
       </c>
@@ -2587,8 +2592,9 @@
       </c>
       <c r="G32" s="80"/>
       <c r="H32" s="80"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="80"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="78" t="s">
         <v>243</v>
       </c>
@@ -2604,8 +2610,9 @@
       </c>
       <c r="G33" s="80"/>
       <c r="H33" s="80"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="80"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="78" t="s">
         <v>246</v>
       </c>
@@ -2621,8 +2628,9 @@
       </c>
       <c r="G34" s="80"/>
       <c r="H34" s="80"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="80"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="78" t="s">
         <v>249</v>
       </c>
@@ -2638,8 +2646,9 @@
       </c>
       <c r="G35" s="80"/>
       <c r="H35" s="80"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="80"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="78" t="s">
         <v>252</v>
       </c>
@@ -2655,6 +2664,7 @@
       </c>
       <c r="G36" s="80"/>
       <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="78" t="s">
@@ -2667,7 +2677,7 @@
       <c r="E38" s="64"/>
       <c r="F38" s="64"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="81" t="s">
         <v>256</v>
       </c>
@@ -2677,29 +2687,30 @@
       <c r="F40" s="81"/>
       <c r="G40" s="81"/>
       <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Microschool_With_Decisions.xlsx
@@ -20,19 +20,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="270">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -393,6 +393,27 @@
     <t>Total Personnel Cost</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION</t>
+  </si>
+  <si>
+    <t>5-Year Total</t>
+  </si>
+  <si>
+    <t>Founder Compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fully-loaded (incl. benefits + payroll tax)</t>
+  </si>
+  <si>
+    <t>Founder Compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t>Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market rate ("sweat equity"). Lenders and boards underwrite to the market-rate line; the adjustment shows the gap.</t>
+  </si>
+  <si>
     <t>INSTRUCTIONAL / PROGRAM</t>
   </si>
   <si>
@@ -460,6 +481,21 @@
   </si>
   <si>
     <t>Cumulative Profit</t>
+  </si>
+  <si>
+    <t>FOUNDER COMPENSATION (memo — already in Personnel above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market ("sweat equity"). Lenders / boards underwrite to the market-rate line.</t>
   </si>
   <si>
     <t>Break-even</t>
@@ -636,7 +672,10 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
+  </si>
+  <si>
+    <t>Built from assumptions</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -835,7 +874,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -933,6 +972,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
@@ -947,6 +992,13 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <color rgb="FF1E293B"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1075,7 +1127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1117,6 +1169,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1124,11 +1182,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1155,10 +1213,11 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1178,7 +1237,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1210,7 +1269,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1999,7 +2058,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2010,691 +2069,702 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="61" t="s">
+      <c r="B3" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D7" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E7" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F7" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="G7" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="62">
-        <v>12</v>
-      </c>
-      <c r="D7" s="62">
-        <v>18</v>
-      </c>
-      <c r="E7" s="62">
-        <v>22</v>
-      </c>
-      <c r="F7" s="62">
-        <v>25</v>
-      </c>
-      <c r="G7" s="62">
-        <v>25</v>
+      <c r="H7" s="64" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="63">
-        <v>221600</v>
-      </c>
-      <c r="D8" s="63">
-        <v>340512</v>
-      </c>
-      <c r="E8" s="63">
-        <v>427946</v>
-      </c>
-      <c r="F8" s="63">
-        <v>500518</v>
-      </c>
-      <c r="G8" s="63">
-        <v>516085</v>
+        <v>214</v>
+      </c>
+      <c r="C8" s="65">
+        <v>12</v>
+      </c>
+      <c r="D8" s="65">
+        <v>18</v>
+      </c>
+      <c r="E8" s="65">
+        <v>22</v>
+      </c>
+      <c r="F8" s="65">
+        <v>25</v>
+      </c>
+      <c r="G8" s="65">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="63">
-        <v>118934</v>
-      </c>
-      <c r="D9" s="63">
-        <v>147003</v>
-      </c>
-      <c r="E9" s="63">
-        <v>151413</v>
-      </c>
-      <c r="F9" s="63">
-        <v>155955</v>
-      </c>
-      <c r="G9" s="63">
-        <v>160634</v>
+        <v>215</v>
+      </c>
+      <c r="C9" s="66">
+        <v>221600</v>
+      </c>
+      <c r="D9" s="66">
+        <v>340512</v>
+      </c>
+      <c r="E9" s="66">
+        <v>427946</v>
+      </c>
+      <c r="F9" s="66">
+        <v>500518</v>
+      </c>
+      <c r="G9" s="66">
+        <v>516085</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="63">
-        <v>48600</v>
-      </c>
-      <c r="D10" s="63">
-        <v>54963</v>
-      </c>
-      <c r="E10" s="63">
-        <v>59946</v>
-      </c>
-      <c r="F10" s="63">
-        <v>64338</v>
-      </c>
-      <c r="G10" s="63">
-        <v>66214</v>
+        <v>216</v>
+      </c>
+      <c r="C10" s="66">
+        <v>118934</v>
+      </c>
+      <c r="D10" s="66">
+        <v>147003</v>
+      </c>
+      <c r="E10" s="66">
+        <v>151413</v>
+      </c>
+      <c r="F10" s="66">
+        <v>155955</v>
+      </c>
+      <c r="G10" s="66">
+        <v>160634</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="63">
+        <v>17</v>
+      </c>
+      <c r="C11" s="66">
+        <v>48600</v>
+      </c>
+      <c r="D11" s="66">
+        <v>54963</v>
+      </c>
+      <c r="E11" s="66">
+        <v>59946</v>
+      </c>
+      <c r="F11" s="66">
+        <v>64338</v>
+      </c>
+      <c r="G11" s="66">
+        <v>66214</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="66">
         <v>6959.808550594178</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D12" s="66">
         <v>6959.808550594178</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E12" s="66">
         <v>6959.808550594178</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F12" s="66">
         <v>6959.808550594178</v>
       </c>
-      <c r="G11" s="63">
+      <c r="G12" s="66">
         <v>6959.808550594178</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="64" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="65">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="68">
         <v>47106</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D13" s="68">
         <v>131586</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E13" s="68">
         <v>209627</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F13" s="68">
         <v>273265</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G13" s="68">
         <v>282277</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="64" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="65">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="67" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="68">
         <v>47106</v>
       </c>
-      <c r="D13" s="65">
+      <c r="D14" s="68">
         <v>178692</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E14" s="68">
         <v>388319</v>
       </c>
-      <c r="F13" s="65">
+      <c r="F14" s="68">
         <v>661584</v>
       </c>
-      <c r="G13" s="65">
+      <c r="G14" s="68">
         <v>943861</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="64" t="s">
-        <v>207</v>
-      </c>
-      <c r="C14" s="66">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="69">
         <v>0.21257220216606498</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D15" s="69">
         <v>0.38643572032703694</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E15" s="69">
         <v>0.4898445130927734</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F15" s="69">
         <v>0.5459643809013862</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G15" s="69">
         <v>0.5469583498842245</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="67">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="70">
         <v>18466.666666666668</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D16" s="70">
         <v>18917.333333333332</v>
       </c>
-      <c r="E15" s="67">
+      <c r="E16" s="70">
         <v>19452.090909090908</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F16" s="70">
         <v>20020.72</v>
       </c>
-      <c r="G15" s="67">
+      <c r="G16" s="70">
         <v>20643.4</v>
       </c>
-      <c r="H15" s="68" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="64" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="69">
+      <c r="H16" s="71" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" s="72">
         <v>14541.150712549514</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D17" s="72">
         <v>11606.989363921899</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E17" s="72">
         <v>9923.582206845189</v>
       </c>
-      <c r="F16" s="69">
+      <c r="F17" s="72">
         <v>9090.112342023767</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G17" s="72">
         <v>9352.312342023766</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C17" s="63">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="66">
         <v>500</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D18" s="66">
         <v>515</v>
       </c>
-      <c r="E17" s="63">
+      <c r="E18" s="66">
         <v>530</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F18" s="66">
         <v>546</v>
       </c>
-      <c r="G17" s="63">
+      <c r="G18" s="66">
         <v>562</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="70">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" s="73">
         <v>3000</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D19" s="73">
         <v>2058.6666666666665</v>
       </c>
-      <c r="E18" s="67">
+      <c r="E19" s="70">
         <v>1733.6818181818182</v>
       </c>
-      <c r="F18" s="67">
+      <c r="F19" s="70">
         <v>1570.1924</v>
       </c>
-      <c r="G18" s="67">
+      <c r="G19" s="70">
         <v>1615.9705720000002</v>
       </c>
-      <c r="H18" s="68" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="71">
+      <c r="H19" s="71" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="74">
         <v>3925.5</v>
       </c>
-      <c r="D19" s="71">
+      <c r="D20" s="74">
         <v>7310.333333333333</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E20" s="74">
         <v>9528.5</v>
       </c>
-      <c r="F19" s="71">
+      <c r="F20" s="74">
         <v>10930.6</v>
       </c>
-      <c r="G19" s="71">
+      <c r="G20" s="74">
         <v>11291.08</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" s="66">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="69">
         <v>0.5367057761732852</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D21" s="69">
         <v>0.43171165773893433</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E21" s="69">
         <v>0.3538133315885649</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F21" s="69">
         <v>0.31158719566529075</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G21" s="69">
         <v>0.3112549289361249</v>
       </c>
-      <c r="H20" s="68" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="72">
+      <c r="H21" s="71" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="75">
         <v>0.1624548736462094</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D22" s="69">
         <v>0.10882435861291231</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E22" s="69">
         <v>0.08912573081650489</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F22" s="69">
         <v>0.07842836821053388</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G22" s="69">
         <v>0.07828025286532257</v>
       </c>
-      <c r="H21" s="68" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="64" t="s">
-        <v>218</v>
-      </c>
-      <c r="C22" s="66">
+      <c r="H22" s="71" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="67" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="69">
         <v>0.24398014440433213</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D23" s="69">
         <v>0.4068755286157316</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E23" s="69">
         <v>0.5061082473022297</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F23" s="69">
         <v>0.5598699747062044</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G23" s="69">
         <v>0.5604445004214422</v>
       </c>
-      <c r="H22" s="68" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="64" t="s">
-        <v>220</v>
-      </c>
-      <c r="C23" s="73">
+      <c r="H23" s="71" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="67" t="s">
+        <v>233</v>
+      </c>
+      <c r="C24" s="76">
         <v>3</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D24" s="76">
         <v>3</v>
       </c>
-      <c r="E23" s="73">
+      <c r="E24" s="76">
         <v>3</v>
       </c>
-      <c r="F23" s="73">
+      <c r="F24" s="76">
         <v>3</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G24" s="76">
         <v>3</v>
       </c>
-      <c r="H23" s="68" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="64" t="s">
-        <v>222</v>
-      </c>
-      <c r="C24" s="74">
+      <c r="H24" s="71" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="77">
         <v>7.768317132140687</v>
       </c>
-      <c r="D24" s="74">
+      <c r="D25" s="77">
         <v>19.906582055072757</v>
       </c>
-      <c r="E24" s="74">
+      <c r="E25" s="77">
         <v>31.11967785112557</v>
       </c>
-      <c r="F24" s="74">
+      <c r="F25" s="77">
         <v>40.26332017079355</v>
       </c>
-      <c r="G24" s="74">
+      <c r="G25" s="77">
         <v>41.558183374930195</v>
       </c>
-      <c r="H24" s="68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="40" t="str">
+      <c r="H25" s="71" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="42" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="75" t="str">
+      <c r="D26" s="78" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="75" t="str">
+      <c r="E26" s="78" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="75" t="str">
+      <c r="F26" s="78" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="75" t="str">
+      <c r="G26" s="78" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="68" t="s">
+      <c r="H26" s="71" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
-        <v>225</v>
-      </c>
-      <c r="C26" s="76">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="79">
         <v>3</v>
       </c>
-      <c r="D26" s="76">
+      <c r="D27" s="79">
         <v>10</v>
       </c>
-      <c r="E26" s="77">
+      <c r="E27" s="80">
         <v>21</v>
       </c>
-      <c r="F26" s="73">
+      <c r="F27" s="76">
         <v>35</v>
       </c>
-      <c r="G26" s="73">
+      <c r="G27" s="76">
         <v>48</v>
       </c>
-      <c r="H26" s="68" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27" s="73">
+      <c r="H27" s="71" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="67" t="s">
+        <v>240</v>
+      </c>
+      <c r="C28" s="76">
         <v>99</v>
       </c>
-      <c r="D27" s="73">
+      <c r="D28" s="76">
         <v>312</v>
       </c>
-      <c r="E27" s="73">
+      <c r="E28" s="76">
         <v>649</v>
       </c>
-      <c r="F27" s="73">
+      <c r="F28" s="76">
         <v>1063</v>
       </c>
-      <c r="G27" s="73">
+      <c r="G28" s="76">
         <v>1473</v>
       </c>
-      <c r="H27" s="68" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="78" t="s">
-        <v>233</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D30" s="79" t="s">
-        <v>235</v>
-      </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="80" t="s">
-        <v>236</v>
-      </c>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
+      <c r="H28" s="71" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="78" t="s">
-        <v>237</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D31" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="E31" s="79"/>
-      <c r="F31" s="80" t="s">
-        <v>239</v>
-      </c>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
+      <c r="B31" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="82" t="s">
+        <v>248</v>
+      </c>
+      <c r="E31" s="82"/>
+      <c r="F31" s="83" t="s">
+        <v>249</v>
+      </c>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="78" t="s">
-        <v>240</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D32" s="79" t="s">
-        <v>241</v>
-      </c>
-      <c r="E32" s="79"/>
-      <c r="F32" s="80" t="s">
-        <v>242</v>
-      </c>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
+      <c r="B32" s="81" t="s">
+        <v>250</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D32" s="82" t="s">
+        <v>251</v>
+      </c>
+      <c r="E32" s="82"/>
+      <c r="F32" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="78" t="s">
-        <v>243</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D33" s="79" t="s">
-        <v>244</v>
-      </c>
-      <c r="E33" s="79"/>
-      <c r="F33" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
+      <c r="B33" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D33" s="82" t="s">
+        <v>254</v>
+      </c>
+      <c r="E33" s="82"/>
+      <c r="F33" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="78" t="s">
-        <v>246</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D34" s="79" t="s">
+      <c r="B34" s="81" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="42" t="s">
         <v>247</v>
       </c>
-      <c r="E34" s="79"/>
-      <c r="F34" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
+      <c r="D34" s="82" t="s">
+        <v>257</v>
+      </c>
+      <c r="E34" s="82"/>
+      <c r="F34" s="83" t="s">
+        <v>258</v>
+      </c>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="78" t="s">
-        <v>249</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D35" s="79" t="s">
-        <v>250</v>
-      </c>
-      <c r="E35" s="79"/>
-      <c r="F35" s="80" t="s">
-        <v>251</v>
-      </c>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="80"/>
+      <c r="B35" s="81" t="s">
+        <v>259</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="82" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35" s="82"/>
+      <c r="F35" s="83" t="s">
+        <v>261</v>
+      </c>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="78" t="s">
-        <v>252</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="D36" s="79" t="s">
-        <v>253</v>
-      </c>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80" t="s">
-        <v>254</v>
-      </c>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="78" t="s">
+      <c r="B36" s="81" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D36" s="82" t="s">
+        <v>263</v>
+      </c>
+      <c r="E36" s="82"/>
+      <c r="F36" s="83" t="s">
+        <v>264</v>
+      </c>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="81" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="82" t="s">
+        <v>266</v>
+      </c>
+      <c r="E37" s="82"/>
+      <c r="F37" s="83" t="s">
+        <v>267</v>
+      </c>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="81" t="s">
-        <v>256</v>
-      </c>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
+      <c r="C39" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="84" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
@@ -2709,95 +2779,97 @@
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:I36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B41:I41"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12:G12">
+  <conditionalFormatting sqref="C13:G13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C12&gt;=0</formula>
+      <formula>C13&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C12&gt;=-1</formula>
+      <formula>C13&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C12&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:G13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C13&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C13&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C13&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:G14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C14&gt;=0.05</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C14&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C14&lt;0</formula>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C14&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C14&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C15&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C15&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C15&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&gt;=10000</formula>
+      <formula>C16&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&gt;=7000</formula>
+      <formula>C16&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&lt;7000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C21&lt;=0.55</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C21&lt;=0.65</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C21&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C22&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C22&lt;=0.22</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C22&gt;0.22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C23&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C25:G25">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C25&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1.15</formula>
+      <formula>C25&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1.15</formula>
+      <formula>C25&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3166,11 +3238,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3478,9 +3550,154 @@
         <v>160634</v>
       </c>
     </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="30">
+        <v>55000</v>
+      </c>
+      <c r="C25" s="30">
+        <v>56650</v>
+      </c>
+      <c r="D25" s="30">
+        <v>58350</v>
+      </c>
+      <c r="E25" s="30">
+        <v>60100</v>
+      </c>
+      <c r="F25" s="30">
+        <v>61903</v>
+      </c>
+      <c r="G25" s="30">
+        <f>SUM(B25:F25)</f>
+        <v>292003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="30">
+        <v>70208</v>
+      </c>
+      <c r="C26" s="30">
+        <v>72314</v>
+      </c>
+      <c r="D26" s="30">
+        <v>74484</v>
+      </c>
+      <c r="E26" s="30">
+        <v>76718</v>
+      </c>
+      <c r="F26" s="30">
+        <v>79019</v>
+      </c>
+      <c r="G26" s="30">
+        <f>SUM(B26:F26)</f>
+        <v>372743</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="30">
+        <v>70000</v>
+      </c>
+      <c r="C27" s="30">
+        <v>72000</v>
+      </c>
+      <c r="D27" s="30">
+        <v>74000</v>
+      </c>
+      <c r="E27" s="30">
+        <v>76000</v>
+      </c>
+      <c r="F27" s="30">
+        <v>79000</v>
+      </c>
+      <c r="G27" s="30">
+        <f>SUM(B27:F27)</f>
+        <v>371000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="30">
+        <v>89355</v>
+      </c>
+      <c r="C28" s="30">
+        <v>91908</v>
+      </c>
+      <c r="D28" s="30">
+        <v>94461</v>
+      </c>
+      <c r="E28" s="30">
+        <v>97014</v>
+      </c>
+      <c r="F28" s="30">
+        <v>100844</v>
+      </c>
+      <c r="G28" s="30">
+        <f>SUM(B28:F28)</f>
+        <v>473582</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="10">
+        <v>19148</v>
+      </c>
+      <c r="C29" s="10">
+        <v>19594</v>
+      </c>
+      <c r="D29" s="10">
+        <v>19977</v>
+      </c>
+      <c r="E29" s="10">
+        <v>20296</v>
+      </c>
+      <c r="F29" s="10">
+        <v>21824</v>
+      </c>
+      <c r="G29" s="10">
+        <f>SUM(B29:F29)</f>
+        <v>100839</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3550,7 +3767,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3560,7 +3777,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B4" s="30">
         <f>500*Assumptions!B23</f>
@@ -3585,7 +3802,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3610,7 +3827,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3620,7 +3837,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B7" s="30">
         <f>300*Assumptions!B23</f>
@@ -3645,7 +3862,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3670,7 +3887,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3680,7 +3897,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B10" s="30">
         <f>2500*12</f>
@@ -3705,7 +3922,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B11" s="30">
         <f>300*12</f>
@@ -3730,7 +3947,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B12" s="30">
         <v>2400</v>
@@ -3750,7 +3967,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
@@ -3775,7 +3992,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3785,7 +4002,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B15" s="30">
         <v>3000</v>
@@ -3805,7 +4022,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B15:B15)</f>
@@ -3830,7 +4047,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B18" s="31">
         <f>B5+B8+B13+B16</f>
@@ -3897,7 +4114,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3907,7 +4124,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B3" s="30">
         <v>6959.808550594178</v>
@@ -3927,7 +4144,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B4" s="31">
         <f>SUM(B3:B3)</f>
@@ -3965,11 +4182,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,7 +4211,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B17</f>
@@ -4019,7 +4236,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B22</f>
@@ -4094,7 +4311,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -4119,7 +4336,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4144,7 +4361,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4171,48 +4388,147 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="41">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>3.2394924753859735</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>10.263461704144051</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="41">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>21.34412488148077</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>34.93466752914153</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="41">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>48.44287620611784</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="41" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="30">
+        <v>70208</v>
+      </c>
+      <c r="C12" s="30">
+        <v>72314</v>
+      </c>
+      <c r="D12" s="30">
+        <v>74484</v>
+      </c>
+      <c r="E12" s="30">
+        <v>76718</v>
+      </c>
+      <c r="F12" s="30">
+        <v>79019</v>
+      </c>
+      <c r="G12" s="30">
+        <f>SUM(B12:F12)</f>
+        <v>372743</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="30">
+        <v>89355</v>
+      </c>
+      <c r="C13" s="30">
+        <v>91908</v>
+      </c>
+      <c r="D13" s="30">
+        <v>94461</v>
+      </c>
+      <c r="E13" s="30">
+        <v>97014</v>
+      </c>
+      <c r="F13" s="30">
+        <v>100844</v>
+      </c>
+      <c r="G13" s="30">
+        <f>SUM(B13:F13)</f>
+        <v>473582</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="10">
+        <v>19148</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19594</v>
+      </c>
+      <c r="D14" s="10">
+        <v>19977</v>
+      </c>
+      <c r="E14" s="10">
+        <v>20296</v>
+      </c>
+      <c r="F14" s="10">
+        <v>21824</v>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(B14:F14)</f>
+        <v>100839</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F16" s="43" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4235,18 +4551,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>143</v>
+      <c r="A2" s="45" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4328,12 +4644,12 @@
         <v>41</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4388,24 +4704,24 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="44">
+        <v>159</v>
+      </c>
+      <c r="C18" s="46">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.5</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="46">
         <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.2222222222222222</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="46">
         <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="F18" s="44" t="str">
+      <c r="F18" s="46" t="str">
         <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0</v>
       </c>
@@ -4432,7 +4748,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B21" s="30">
         <f>'Financial Model'!B2</f>
@@ -4457,7 +4773,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
@@ -4507,7 +4823,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
@@ -4532,32 +4848,32 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="45">
+        <v>145</v>
+      </c>
+      <c r="B25" s="47">
         <f>'Financial Model'!B7</f>
         <v>47106</v>
       </c>
-      <c r="C25" s="45">
+      <c r="C25" s="47">
         <f>'Financial Model'!C7</f>
         <v>131586</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="47">
         <f>'Financial Model'!D7</f>
         <v>209627</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="47">
         <f>'Financial Model'!E7</f>
         <v>273265</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="47">
         <f>'Financial Model'!F7</f>
         <v>282277</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
@@ -4607,7 +4923,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4617,7 +4933,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B30" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -4642,57 +4958,57 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="44">
+        <v>162</v>
+      </c>
+      <c r="B31" s="46">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
         <v>0.5367057761732852</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="46">
         <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
         <v>0.43171165773893433</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="46">
         <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
         <v>0.3538133315885649</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="46">
         <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
         <v>0.31158719566529075</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="46">
         <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
         <v>0.3112549289361249</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B32" s="44">
+        <v>163</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.21931407942238268</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="46">
         <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.16141281364533408</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="46">
         <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.14007842110920538</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="46">
         <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.12854282962850486</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="46">
         <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.12830057064243294</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B33" s="12">
         <f>IF(B21=0,0,B25/B21)</f>
@@ -4717,7 +5033,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4727,61 +5043,61 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B36" s="44">
+        <v>166</v>
+      </c>
+      <c r="B36" s="46">
         <v>0.5983754512635379</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="46">
         <v>0.6012475331265859</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="46">
         <v>0.6018841638357006</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="46">
         <v>0.6019619693617106</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="46">
         <v>0.6009378300086227</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B37" s="44">
+        <v>167</v>
+      </c>
+      <c r="B37" s="46">
         <v>0.37906137184115524</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="46">
         <v>0.3811319424866084</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="46">
         <v>0.3817586245734857</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="46">
         <v>0.38205457351641053</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="46">
         <v>0.3816231822277338</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B38" s="44">
+        <v>168</v>
+      </c>
+      <c r="B38" s="46">
         <v>0.02256317689530686</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="46">
         <v>0.017620524386805753</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="46">
         <v>0.016357211590813603</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="46">
         <v>0.015983457121878854</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="46">
         <v>0.017438987763643585</v>
       </c>
     </row>
@@ -4829,169 +5145,169 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" ht="44" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="B2" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="47" t="s">
+      <c r="B4" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="47" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="H4" s="47" t="s">
-        <v>163</v>
+      <c r="D4" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="H5" s="50" t="s">
-        <v>170</v>
+      <c r="A5" s="50"/>
+      <c r="B5" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="48"/>
-      <c r="B6" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="G6" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="50" t="s">
-        <v>176</v>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="54" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="F7" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="G7" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>183</v>
+      <c r="A7" s="55"/>
+      <c r="B7" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="49" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="H8" s="50" t="s">
-        <v>188</v>
+      <c r="D8" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="B9" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9" s="52" t="s">
+      <c r="A9" s="57"/>
+      <c r="B9" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="G9" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="H9" s="50" t="s">
+      <c r="D9" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="52" t="s">
         <v>192</v>
       </c>
+      <c r="F9" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
+      <c r="B11" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="3">
